--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Germany Bundesliga_20242025.xlsx
@@ -12934,13 +12934,13 @@
         <v>6</v>
       </c>
       <c r="BA57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB57" t="n">
         <v>3</v>
       </c>
       <c r="BC57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD57" t="n">
         <v>1.24</v>
@@ -13370,13 +13370,13 @@
         <v>9</v>
       </c>
       <c r="BA59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC59" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BD59" t="n">
         <v>1.7</v>
